--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrFund003MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrFund003MTM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zhaoyin\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cms\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>序号</t>
   </si>
@@ -58,29 +58,17 @@
   </si>
   <si>
     <t>转入资产代码</t>
-  </si>
-  <si>
-    <t>指令数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -114,14 +102,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -399,16 +384,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="14.6328125" customWidth="1"/>
-    <col min="12" max="12" width="22.6328125" customWidth="1"/>
-    <col min="13" max="13" width="9.08984375" customWidth="1"/>
-    <col min="14" max="17" width="14.6328125" customWidth="1"/>
+    <col min="1" max="10" width="14.6328125" customWidth="1"/>
+    <col min="11" max="11" width="22.6328125" customWidth="1"/>
+    <col min="12" max="12" width="9.08984375" customWidth="1"/>
+    <col min="13" max="16" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,38 +415,35 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>13</v>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F101">
       <formula1>"T01:买入,T02:卖出,T04:申购,T06:赎回,T52:认购,T65:转换申请"</formula1>
